--- a/data/raw/sales/Week 27/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 27/Tonor/Vendor Sales (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,13 +531,13 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
-        <v>20921.16</v>
+        <v>45597.36</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8900</v>
+        <v>13050.84</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29519.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
-      </c>
-      <c r="I4" t="n">
-        <v>27447.37</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -692,7 +692,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -795,10 +795,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3388.14</v>
+        <v>5110.17</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -824,19 +824,19 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FBA77105</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,10 +864,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2372.03</v>
+        <v>1927.97</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -890,19 +890,19 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA77105</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -912,34 +912,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tripod</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>22393.23</v>
+        <v>2372.03</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -978,34 +978,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Tripod</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>12783.91</v>
+        <v>29350.86</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1022,19 +1022,19 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1044,34 +1044,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boom Arm Kit + RGB</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>17697.47</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1088,19 +1088,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FBA79111</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1110,34 +1110,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TD510</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USB/XLR Mic</t>
+          <t>Boom Arm Kit + RGB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>10166.94</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1154,19 +1154,19 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1176,28 +1176,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>USB/XLR Mic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>23886.44</v>
+        <v>13428.8</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1220,19 +1220,19 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB - RGB</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1260,16 +1260,16 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2456.78</v>
+        <v>1948.31</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1286,19 +1286,19 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79116</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1308,28 +1308,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TC-777 PRO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Low Profile Boom Arm</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>32568.64</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1352,19 +1352,19 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79114</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1374,34 +1374,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>TC310+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Boom Arm Kit - USB - RGB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7116.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>1863.56</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1418,19 +1418,19 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA79585</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1440,51 +1440,249 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>T20LP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hand held Mic + Stand</t>
+          <t>Low Profile Boom Arm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3472.88</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>27</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B0CQX3VB1R</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FBA79696</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TD310+</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dynamic Microphone</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hand held Mic + Boom Arm</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1863.56</v>
+      </c>
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>6441.51</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>27</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B0CQX4K9P5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FBA79697</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dynamic Microphone</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hand held Mic + Stand</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12882.19</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1p Sales</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>27</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>27</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B0CSCT63BL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FBA79577</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TM310</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Conference Microphone</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Wired</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1948.31</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>27</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
